--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="206">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:22+00:00</t>
+    <t>2026-04-24T13:15:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -621,6 +621,10 @@
   </si>
   <si>
     <t>fr-lm-condition.bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-body-structure
+</t>
   </si>
   <si>
     <t>Localisation anatomique</t>
@@ -4138,13 +4142,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>131</v>
+        <v>194</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4212,10 +4216,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4241,10 +4245,10 @@
         <v>131</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4295,7 +4299,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4312,10 +4316,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4341,10 +4345,10 @@
         <v>131</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4374,10 +4378,10 @@
         <v>73</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>73</v>
@@ -4395,7 +4399,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4412,10 +4416,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4441,10 +4445,10 @@
         <v>168</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4495,7 +4499,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -4512,10 +4516,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4541,10 +4545,10 @@
         <v>153</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4595,7 +4599,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:15:59+00:00</t>
+    <t>2026-04-29T08:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,11 +269,11 @@
     <t>fr-lm-condition.header.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
 </t>
   </si>
   <si>
-    <t>Patient/subject information</t>
+    <t>Patient / Usager</t>
   </si>
   <si>
     <t>fr-lm-entry.header.subject</t>
@@ -443,7 +443,7 @@
     <t>fr-lm-entry.header.source</t>
   </si>
   <si>
-    <t>fr-lm-condition.header.langue</t>
+    <t>fr-lm-condition.header.language</t>
   </si>
   <si>
     <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
@@ -451,7 +451,7 @@
 La partie en majuscules indique le code pays (ISO-3166)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.langue</t>
+    <t>fr-lm-entry.header.language</t>
   </si>
   <si>
     <t>fr-lm-condition.type</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="203">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -422,13 +422,16 @@
 </t>
   </si>
   <si>
-    <t>Statut de l'acte</t>
-  </si>
-  <si>
-    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+    <t>Statut du problème</t>
+  </si>
+  <si>
+    <t>Statut</t>
+  </si>
+  <si>
+    <t>Valeur issue du jdv-hl7-condition-clinical-cisis (2.16.840.1.113883.4.642.3.164)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-condition-clinical-cisis</t>
   </si>
   <si>
     <t>fr-lm-entry.header.status</t>
@@ -600,18 +603,6 @@
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-severite-observation-cisis</t>
-  </si>
-  <si>
-    <t>fr-lm-condition.conditionStatus</t>
-  </si>
-  <si>
-    <t>Statut du problème</t>
-  </si>
-  <si>
-    <t>Valeur issue du jdv-hl7-condition-clinical-cisis (2.16.840.1.113883.4.642.3.164)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-condition-clinical-cisis</t>
   </si>
   <si>
     <t>fr-lm-condition.clinicalStatus</t>
@@ -960,7 +951,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ36"/>
+  <dimension ref="A1:AJ35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.79296875" customWidth="true" bestFit="true"/>
@@ -2623,7 +2614,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>79</v>
@@ -2644,7 +2635,7 @@
         <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2674,10 +2665,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2695,10 +2686,10 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>79</v>
@@ -2712,10 +2703,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2741,10 +2732,10 @@
         <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2795,7 +2786,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2812,10 +2803,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2841,10 +2832,10 @@
         <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2895,7 +2886,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2912,10 +2903,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2941,10 +2932,10 @@
         <v>131</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2974,10 +2965,10 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -2995,7 +2986,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3012,10 +3003,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3041,10 +3032,10 @@
         <v>131</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3095,7 +3086,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3112,10 +3103,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3138,13 +3129,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3195,7 +3186,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3207,15 +3198,15 @@
         <v>73</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3238,13 +3229,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3295,7 +3286,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3312,14 +3303,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -3338,16 +3329,16 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3385,19 +3376,19 @@
         <v>73</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3409,15 +3400,15 @@
         <v>73</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3440,16 +3431,16 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3499,7 +3490,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -3516,10 +3507,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3542,13 +3533,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3599,7 +3590,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3611,15 +3602,15 @@
         <v>73</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3645,10 +3636,10 @@
         <v>127</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3699,7 +3690,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3716,10 +3707,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3745,10 +3736,10 @@
         <v>127</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3799,7 +3790,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3816,10 +3807,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3845,10 +3836,10 @@
         <v>131</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3878,10 +3869,10 @@
         <v>73</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>73</v>
@@ -3899,7 +3890,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3916,10 +3907,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3945,10 +3936,10 @@
         <v>131</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3978,10 +3969,10 @@
         <v>73</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>189</v>
+        <v>73</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>190</v>
+        <v>73</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>73</v>
@@ -3999,7 +3990,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4016,10 +4007,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4030,7 +4021,7 @@
         <v>74</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>73</v>
@@ -4042,7 +4033,7 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>192</v>
@@ -4099,13 +4090,13 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>73</v>
@@ -4142,13 +4133,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="L32" t="s" s="2">
-        <v>195</v>
-      </c>
       <c r="M32" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4216,10 +4207,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4230,7 +4221,7 @@
         <v>74</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>73</v>
@@ -4245,10 +4236,10 @@
         <v>131</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4278,10 +4269,10 @@
         <v>73</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>73</v>
+        <v>197</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>73</v>
+        <v>198</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>73</v>
@@ -4299,13 +4290,13 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>73</v>
@@ -4316,10 +4307,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4327,10 +4318,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>73</v>
@@ -4342,13 +4333,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4378,10 +4369,10 @@
         <v>73</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>200</v>
+        <v>73</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>201</v>
+        <v>73</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>73</v>
@@ -4399,13 +4390,13 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>73</v>
@@ -4416,10 +4407,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4427,10 +4418,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>73</v>
@@ -4442,13 +4433,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4499,118 +4490,18 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K36" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
-      <c r="P36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q36" s="2"/>
-      <c r="R36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
